--- a/171/food/2026-01-19-sm.xlsx
+++ b/171/food/2026-01-19-sm.xlsx
@@ -320,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -421,10 +421,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -844,8 +841,8 @@
           <t>МБОУ "СОШ им.Б.Н.Жабраилова с. Шовхал-Берды"</t>
         </is>
       </c>
-      <c r="C1" s="40" t="n"/>
-      <c r="D1" s="41" t="n"/>
+      <c r="C1" s="39" t="n"/>
+      <c r="D1" s="40" t="n"/>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Отд./корп</t>
@@ -860,7 +857,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>19.01.2026</t>
         </is>
       </c>
     </row>
@@ -934,7 +931,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
@@ -943,21 +940,21 @@
         </is>
       </c>
       <c r="E4" s="21" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F4" s="22" t="n">
         <v>13.77</v>
       </c>
-      <c r="G4" s="42" t="n">
-        <v>59.7</v>
+      <c r="G4" s="21" t="n">
+        <v>60</v>
       </c>
       <c r="H4" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="I4" s="42" t="n">
+      <c r="I4" s="41" t="n">
         <v>0.5</v>
       </c>
-      <c r="J4" s="43" t="n">
+      <c r="J4" s="42" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -975,25 +972,25 @@
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Рис отварной</t>
+          <t>Рис отварной №304</t>
         </is>
       </c>
       <c r="E5" s="28" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>18.35</v>
       </c>
-      <c r="G5" s="44" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="H5" s="44" t="n">
+      <c r="G5" s="28" t="n">
+        <v>130</v>
+      </c>
+      <c r="H5" s="43" t="n">
         <v>2.4</v>
       </c>
-      <c r="I5" s="44" t="n">
+      <c r="I5" s="43" t="n">
         <v>3.6</v>
       </c>
-      <c r="J5" s="45" t="n">
+      <c r="J5" s="44" t="n">
         <v>24.5</v>
       </c>
     </row>
@@ -1004,32 +1001,14 @@
           <t>гор.напиток</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>Чай с лимоном</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>39</v>
-      </c>
+      <c r="C6" s="27" t="e"/>
+      <c r="D6" s="26" t="e"/>
+      <c r="E6" s="32" t="e"/>
+      <c r="F6" s="32" t="e"/>
+      <c r="G6" s="32" t="e"/>
       <c r="H6" s="32" t="e"/>
-      <c r="I6" s="44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J6" s="45" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="I6" s="32" t="e"/>
+      <c r="J6" s="33" t="e"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="25" t="e"/>
@@ -1038,11 +1017,7 @@
           <t>хлеб</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
+      <c r="C7" s="27" t="e"/>
       <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Хлеб пшеничный</t>
@@ -1052,18 +1027,18 @@
         <v>50</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="G7" s="44" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="H7" s="44" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>109</v>
+      </c>
+      <c r="H7" s="43" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" s="44" t="n">
+      <c r="I7" s="43" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="45" t="n">
+      <c r="J7" s="44" t="n">
         <v>24.1</v>
       </c>
     </row>
@@ -1087,72 +1062,68 @@
       <c r="A9" s="25" t="e"/>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>кисломол.</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>сладкое</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="e"/>
       <c r="D9" s="26" t="inlineStr">
         <is>
-          <t>Масло сливочное (порциями)</t>
+          <t>Булочка домашняя</t>
         </is>
       </c>
       <c r="E9" s="28" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G9" s="44" t="n">
-        <v>111.9</v>
-      </c>
-      <c r="H9" s="44" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I9" s="44" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J9" s="45" t="n">
-        <v>0.2</v>
+        <v>11.01</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>172</v>
+      </c>
+      <c r="H9" s="43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I9" s="43" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>27.8</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="25" t="e"/>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>булочное</t>
+          <t>кисломол.</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Булочка </t>
+          <t>Масло сливочное (порциями) №14</t>
         </is>
       </c>
       <c r="E10" s="28" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="G10" s="44" t="n">
-        <v>118.8</v>
-      </c>
-      <c r="H10" s="44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I10" s="44" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J10" s="45" t="n">
-        <v>9.6</v>
+        <v>2.75</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>116</v>
+      </c>
+      <c r="H10" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="43" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
@@ -1166,14 +1137,34 @@
           <t>закуска</t>
         </is>
       </c>
-      <c r="C11" s="19" t="e"/>
-      <c r="D11" s="20" t="e"/>
-      <c r="E11" s="34" t="e"/>
-      <c r="F11" s="34" t="e"/>
-      <c r="G11" s="34" t="e"/>
-      <c r="H11" s="34" t="e"/>
-      <c r="I11" s="34" t="e"/>
-      <c r="J11" s="35" t="e"/>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>Салат из квашеной капусты с луком №9</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>103</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>8.199999999999999</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="25" t="e"/>
@@ -1182,14 +1173,34 @@
           <t>1 блюдо</t>
         </is>
       </c>
-      <c r="C12" s="27" t="e"/>
-      <c r="D12" s="26" t="e"/>
-      <c r="E12" s="32" t="e"/>
-      <c r="F12" s="32" t="e"/>
-      <c r="G12" s="32" t="e"/>
-      <c r="H12" s="32" t="e"/>
-      <c r="I12" s="32" t="e"/>
-      <c r="J12" s="33" t="e"/>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Борщ со свежей капустой и томатом №83</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>205</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>114</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" s="34" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="25" t="e"/>
@@ -1198,14 +1209,34 @@
           <t>2 блюдо</t>
         </is>
       </c>
-      <c r="C13" s="27" t="e"/>
-      <c r="D13" s="26" t="e"/>
-      <c r="E13" s="32" t="e"/>
-      <c r="F13" s="32" t="e"/>
-      <c r="G13" s="32" t="e"/>
-      <c r="H13" s="32" t="e"/>
-      <c r="I13" s="32" t="e"/>
-      <c r="J13" s="33" t="e"/>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Макаронные изделия отварные с маслом №203</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="n">
+        <v>120</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <v>196</v>
+      </c>
+      <c r="H13" s="43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I13" s="43" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J13" s="44" t="n">
+        <v>30.5</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="25" t="e"/>
@@ -1230,14 +1261,32 @@
           <t>напиток</t>
         </is>
       </c>
-      <c r="C15" s="27" t="e"/>
-      <c r="D15" s="26" t="e"/>
-      <c r="E15" s="32" t="e"/>
-      <c r="F15" s="32" t="e"/>
-      <c r="G15" s="32" t="e"/>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Чай с лимоном №459</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>39</v>
+      </c>
       <c r="H15" s="32" t="e"/>
-      <c r="I15" s="32" t="e"/>
-      <c r="J15" s="33" t="e"/>
+      <c r="I15" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="44" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="25" t="e"/>
@@ -1247,29 +1296,65 @@
         </is>
       </c>
       <c r="C16" s="27" t="e"/>
-      <c r="D16" s="26" t="e"/>
-      <c r="E16" s="32" t="e"/>
-      <c r="F16" s="32" t="e"/>
-      <c r="G16" s="32" t="e"/>
-      <c r="H16" s="32" t="e"/>
-      <c r="I16" s="32" t="e"/>
-      <c r="J16" s="33" t="e"/>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Хлеб пшеничный</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="43" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>185</v>
+      </c>
+      <c r="H16" s="43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I16" s="43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J16" s="44" t="n">
+        <v>33.8</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="25" t="e"/>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>хлеб черн.</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="e"/>
-      <c r="D17" s="26" t="e"/>
-      <c r="E17" s="32" t="e"/>
-      <c r="F17" s="32" t="e"/>
-      <c r="G17" s="32" t="e"/>
-      <c r="H17" s="32" t="e"/>
-      <c r="I17" s="32" t="e"/>
-      <c r="J17" s="33" t="e"/>
+          <t>кисломол.</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Масло сливочное (порциями) №14</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>98</v>
+      </c>
+      <c r="H17" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="43" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J17" s="44" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="25" t="e"/>
@@ -1284,16 +1369,16 @@
       <c r="J18" s="33" t="e"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="36" t="e"/>
-      <c r="B19" s="37" t="e"/>
-      <c r="C19" s="38" t="e"/>
-      <c r="D19" s="37" t="e"/>
-      <c r="E19" s="38" t="e"/>
-      <c r="F19" s="38" t="e"/>
-      <c r="G19" s="38" t="e"/>
-      <c r="H19" s="38" t="e"/>
-      <c r="I19" s="38" t="e"/>
-      <c r="J19" s="39" t="e"/>
+      <c r="A19" s="35" t="e"/>
+      <c r="B19" s="36" t="e"/>
+      <c r="C19" s="37" t="e"/>
+      <c r="D19" s="36" t="e"/>
+      <c r="E19" s="37" t="e"/>
+      <c r="F19" s="37" t="e"/>
+      <c r="G19" s="37" t="e"/>
+      <c r="H19" s="37" t="e"/>
+      <c r="I19" s="37" t="e"/>
+      <c r="J19" s="38" t="e"/>
     </row>
   </sheetData>
   <mergeCells count="1">
